--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40530,6 +40530,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1747" t="n">
+        <v>233119</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>17</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>16.2099990844727</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>16.3700008392334</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>16.9899997711182</v>
+      </c>
+      <c r="G1747" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40553,6 +40553,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>230225</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>17.6000003814697</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>16.7999992370605</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="G1748" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40576,6 +40576,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>355225</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>18.8500003814697</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>17.0499992370605</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>18.7800006866455</v>
+      </c>
+      <c r="G1749" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40599,6 +40599,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>393089</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>19.9899997711182</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>18.8199996948242</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="G1750" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40440,22 +40440,22 @@
     </row>
     <row r="1743">
       <c r="A1743" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1743" t="n">
-        <v>177242</v>
+        <v>84310</v>
       </c>
       <c r="C1743" t="n">
-        <v>16.3999996185303</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="D1743" t="n">
-        <v>15.9099998474121</v>
+        <v>15.6499996185303</v>
       </c>
       <c r="E1743" t="n">
-        <v>15.9200000762939</v>
+        <v>15.8100004196167</v>
       </c>
       <c r="F1743" t="n">
-        <v>16.1499996185303</v>
+        <v>15.9799995422363</v>
       </c>
       <c r="G1743" t="s">
         <v>7</v>
@@ -40463,22 +40463,22 @@
     </row>
     <row r="1744">
       <c r="A1744" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1744" t="n">
-        <v>186032</v>
+        <v>177242</v>
       </c>
       <c r="C1744" t="n">
         <v>16.3999996185303</v>
       </c>
       <c r="D1744" t="n">
-        <v>15.9499998092651</v>
+        <v>15.9099998474121</v>
       </c>
       <c r="E1744" t="n">
-        <v>16.1399993896484</v>
+        <v>15.9200000762939</v>
       </c>
       <c r="F1744" t="n">
-        <v>16</v>
+        <v>16.1499996185303</v>
       </c>
       <c r="G1744" t="s">
         <v>7</v>
@@ -40486,22 +40486,22 @@
     </row>
     <row r="1745">
       <c r="A1745" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1745" t="n">
-        <v>129072</v>
+        <v>186032</v>
       </c>
       <c r="C1745" t="n">
-        <v>16.3600006103516</v>
+        <v>16.3999996185303</v>
       </c>
       <c r="D1745" t="n">
         <v>15.9499998092651</v>
       </c>
       <c r="E1745" t="n">
-        <v>15.960000038147</v>
+        <v>16.1399993896484</v>
       </c>
       <c r="F1745" t="n">
-        <v>16.1800003051758</v>
+        <v>16</v>
       </c>
       <c r="G1745" t="s">
         <v>7</v>
@@ -40509,22 +40509,22 @@
     </row>
     <row r="1746">
       <c r="A1746" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1746" t="n">
-        <v>103038</v>
+        <v>129072</v>
       </c>
       <c r="C1746" t="n">
-        <v>16.3299999237061</v>
+        <v>16.3600006103516</v>
       </c>
       <c r="D1746" t="n">
-        <v>16.0499992370605</v>
+        <v>15.9499998092651</v>
       </c>
       <c r="E1746" t="n">
+        <v>15.960000038147</v>
+      </c>
+      <c r="F1746" t="n">
         <v>16.1800003051758</v>
-      </c>
-      <c r="F1746" t="n">
-        <v>16.3299999237061</v>
       </c>
       <c r="G1746" t="s">
         <v>7</v>
@@ -40532,22 +40532,22 @@
     </row>
     <row r="1747">
       <c r="A1747" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1747" t="n">
-        <v>233119</v>
+        <v>103038</v>
       </c>
       <c r="C1747" t="n">
-        <v>17</v>
+        <v>16.3299999237061</v>
       </c>
       <c r="D1747" t="n">
-        <v>16.2099990844727</v>
+        <v>16.0499992370605</v>
       </c>
       <c r="E1747" t="n">
-        <v>16.3700008392334</v>
+        <v>16.1800003051758</v>
       </c>
       <c r="F1747" t="n">
-        <v>16.9899997711182</v>
+        <v>16.3299999237061</v>
       </c>
       <c r="G1747" t="s">
         <v>7</v>
@@ -40555,22 +40555,22 @@
     </row>
     <row r="1748">
       <c r="A1748" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1748" t="n">
-        <v>230225</v>
+        <v>233119</v>
       </c>
       <c r="C1748" t="n">
-        <v>17.6000003814697</v>
+        <v>17</v>
       </c>
       <c r="D1748" t="n">
-        <v>16.7999992370605</v>
+        <v>16.2099990844727</v>
       </c>
       <c r="E1748" t="n">
-        <v>17.2999992370605</v>
+        <v>16.3700008392334</v>
       </c>
       <c r="F1748" t="n">
-        <v>17.25</v>
+        <v>16.9899997711182</v>
       </c>
       <c r="G1748" t="s">
         <v>7</v>
@@ -40578,22 +40578,22 @@
     </row>
     <row r="1749">
       <c r="A1749" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1749" t="n">
-        <v>355225</v>
+        <v>230225</v>
       </c>
       <c r="C1749" t="n">
-        <v>18.8500003814697</v>
+        <v>17.6000003814697</v>
       </c>
       <c r="D1749" t="n">
-        <v>17.0499992370605</v>
+        <v>16.7999992370605</v>
       </c>
       <c r="E1749" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F1749" t="n">
         <v>17.25</v>
-      </c>
-      <c r="F1749" t="n">
-        <v>18.7800006866455</v>
       </c>
       <c r="G1749" t="s">
         <v>7</v>
@@ -40601,24 +40601,47 @@
     </row>
     <row r="1750">
       <c r="A1750" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1750" t="n">
-        <v>393089</v>
+        <v>355225</v>
       </c>
       <c r="C1750" t="n">
-        <v>19.9899997711182</v>
+        <v>18.8500003814697</v>
       </c>
       <c r="D1750" t="n">
-        <v>18.8199996948242</v>
+        <v>17.0499992370605</v>
       </c>
       <c r="E1750" t="n">
-        <v>18.8999996185303</v>
+        <v>17.25</v>
       </c>
       <c r="F1750" t="n">
-        <v>19.1000003814697</v>
+        <v>18.7800006866455</v>
       </c>
       <c r="G1750" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>314151</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>19</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>17.6800003051758</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>18.9599990844727</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G1751" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -45953,6 +45953,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1754" t="n">
+        <v>100900</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>18.6599998474121</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>18.4799995422363</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>18.4300003051758</v>
+      </c>
+      <c r="G1754" t="n">
+        <v>18.4300003051758</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -45979,6 +45979,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1755" t="n">
+        <v>73894</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>17.9799995422363</v>
+      </c>
+      <c r="G1755" t="n">
+        <v>17.9799995422363</v>
+      </c>
+      <c r="H1755" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -45990,7 +45990,7 @@
         <v>18.5</v>
       </c>
       <c r="D1755" t="n">
-        <v>18.0499992370605</v>
+        <v>17.9799995422363</v>
       </c>
       <c r="E1755" t="n">
         <v>18.5</v>
@@ -46002,6 +46002,32 @@
         <v>17.9799995422363</v>
       </c>
       <c r="H1755" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1756" t="n">
+        <v>86454</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>17.8299999237061</v>
+      </c>
+      <c r="G1756" t="n">
+        <v>17.8299999237061</v>
+      </c>
+      <c r="H1756" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -46031,6 +46031,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>151390</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="H1757" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -46109,6 +46109,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1760" t="n">
+        <v>79742</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>18.8299999237061</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>18.2700004577637</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>18.4500007629395</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>18.3700008392334</v>
+      </c>
+      <c r="G1760" t="n">
+        <v>18.3700008392334</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40914,8 +40914,31 @@
       <c r="E1763" t="n">
         <v>17.4300003051758</v>
       </c>
-      <c r="F1763"/>
+      <c r="F1763" t="n">
+        <v>17.7600002288818</v>
+      </c>
       <c r="G1763" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1764" t="n">
+        <v>36871</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>17.9300003051758</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>17.5400009155273</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>17.5400009155273</v>
+      </c>
+      <c r="F1764"/>
+      <c r="G1764" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40937,8 +40937,31 @@
       <c r="E1764" t="n">
         <v>17.5400009155273</v>
       </c>
-      <c r="F1764"/>
+      <c r="F1764" t="n">
+        <v>17.8600006103516</v>
+      </c>
       <c r="G1764" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1765" t="n">
+        <v>94617</v>
+      </c>
+      <c r="C1765" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>17.6399993896484</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>17.9699993133545</v>
+      </c>
+      <c r="F1765"/>
+      <c r="G1765" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40960,8 +40960,31 @@
       <c r="E1765" t="n">
         <v>17.9699993133545</v>
       </c>
-      <c r="F1765"/>
+      <c r="F1765" t="n">
+        <v>17.7299995422363</v>
+      </c>
       <c r="G1765" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1766" t="n">
+        <v>44957</v>
+      </c>
+      <c r="C1766" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>17.4200000762939</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="F1766"/>
+      <c r="G1766" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -40983,8 +40983,31 @@
       <c r="E1766" t="n">
         <v>17.8999996185303</v>
       </c>
-      <c r="F1766"/>
+      <c r="F1766" t="n">
+        <v>17.5599994659424</v>
+      </c>
       <c r="G1766" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1767" t="n">
+        <v>118550</v>
+      </c>
+      <c r="C1767" t="n">
+        <v>18.4200000762939</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>17.3700008392334</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>17.3700008392334</v>
+      </c>
+      <c r="F1767"/>
+      <c r="G1767" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -41013,6 +41013,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1768">
+      <c r="A1768" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1768" t="n">
+        <v>223195</v>
+      </c>
+      <c r="C1768" t="n">
+        <v>19.2399997711182</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>17.8899993896484</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>19.0599994659424</v>
+      </c>
+      <c r="G1768" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -46395,6 +46395,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1771">
+      <c r="A1771" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1771" t="n">
+        <v>137980</v>
+      </c>
+      <c r="C1771" t="n">
+        <v>21.8400001525879</v>
+      </c>
+      <c r="D1771" t="n">
+        <v>21.0400009155273</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>21.2800006866455</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>21.5599994659424</v>
+      </c>
+      <c r="G1771" t="n">
+        <v>21.5599994659424</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -46421,6 +46421,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1772">
+      <c r="A1772" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1772" t="n">
+        <v>58680</v>
+      </c>
+      <c r="C1772" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>20.8600006103516</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>21.2800006866455</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>21.1200008392334</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>21.1200008392334</v>
+      </c>
+      <c r="H1772" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51766,6 +51766,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1773">
+      <c r="A1773" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1773" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1773" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>21.3600006103516</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>20.0799999237061</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>20.2999992370605</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>20.2999992370605</v>
+      </c>
+      <c r="H1773" t="n">
+        <v>96317</v>
+      </c>
+      <c r="I1773" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1774" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1774" t="n">
+        <v>20.2800006866455</v>
+      </c>
+      <c r="D1774" t="n">
+        <v>20.7399997711182</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>20.2399997711182</v>
+      </c>
+      <c r="F1774" t="n">
+        <v>20.6200008392334</v>
+      </c>
+      <c r="G1774" t="n">
+        <v>20.6200008392334</v>
+      </c>
+      <c r="H1774" t="n">
+        <v>65893</v>
+      </c>
+      <c r="I1774" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51824,6 +51824,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1775">
+      <c r="A1775" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1775" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1775" t="n">
+        <v>20.7999992370605</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>21.4400005340576</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>20.4799995422363</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>21.4400005340576</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>21.4400005340576</v>
+      </c>
+      <c r="H1775" t="n">
+        <v>89009</v>
+      </c>
+      <c r="I1775" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51853,6 +51853,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1776">
+      <c r="A1776" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1776" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1776" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>21.6800003051758</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>21.1200008392334</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>21.1200008392334</v>
+      </c>
+      <c r="H1776" t="n">
+        <v>54712</v>
+      </c>
+      <c r="I1776" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51882,6 +51882,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1777">
+      <c r="A1777" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1777" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1777" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>20.9200000762939</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="H1777" t="n">
+        <v>55966</v>
+      </c>
+      <c r="I1777" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51896,7 +51896,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="E1777" t="n">
-        <v>20.9200000762939</v>
+        <v>20.8999996185303</v>
       </c>
       <c r="F1777" t="n">
         <v>21.6000003814697</v>
@@ -51908,6 +51908,35 @@
         <v>55966</v>
       </c>
       <c r="I1777" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1778" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1778" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>21.7199993133545</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>21.0599994659424</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>21.6200008392334</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>21.6200008392334</v>
+      </c>
+      <c r="H1778" t="n">
+        <v>63817</v>
+      </c>
+      <c r="I1778" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51940,6 +51940,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1779">
+      <c r="A1779" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1779" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1779" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="D1779" t="n">
+        <v>22.1200008392334</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>21.3199996948242</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>21.8600006103516</v>
+      </c>
+      <c r="G1779" t="n">
+        <v>21.8600006103516</v>
+      </c>
+      <c r="H1779" t="n">
+        <v>86760</v>
+      </c>
+      <c r="I1779" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51969,6 +51969,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1780">
+      <c r="A1780" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1780" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1780" t="n">
+        <v>21.6200008392334</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>22.4200000762939</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>21.4200000762939</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>21.4200000762939</v>
+      </c>
+      <c r="G1780" t="n">
+        <v>21.4200000762939</v>
+      </c>
+      <c r="H1780" t="n">
+        <v>74066</v>
+      </c>
+      <c r="I1780" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -51998,6 +51998,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1781">
+      <c r="A1781" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1781" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1781" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>22.2800006866455</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>21.5200004577637</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>22</v>
+      </c>
+      <c r="G1781" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1781" t="n">
+        <v>72633</v>
+      </c>
+      <c r="I1781" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NWL.MI.xlsx
+++ b/data/NWL.MI.xlsx
@@ -52021,9 +52021,38 @@
         <v>22</v>
       </c>
       <c r="H1781" t="n">
-        <v>72633</v>
+        <v>72837</v>
       </c>
       <c r="I1781" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1782" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1782" t="n">
+        <v>22.2600002288818</v>
+      </c>
+      <c r="D1782" t="n">
+        <v>22.4400005340576</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>21.7600002288818</v>
+      </c>
+      <c r="F1782" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="G1782" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="H1782" t="n">
+        <v>62350</v>
+      </c>
+      <c r="I1782" t="s">
         <v>9</v>
       </c>
     </row>
